--- a/budget-tracker/Budget-Tracker.xlsx
+++ b/budget-tracker/Budget-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="130">
   <si>
     <t>BUDGET TRACKER</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Betrag</t>
+  </si>
+  <si>
+    <t>DIAGRAMME</t>
   </si>
   <si>
     <t>Powered by Budget Tracker Pro · All data updates automatically</t>
@@ -925,7 +928,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1075,6 +1078,7 @@
     <xf numFmtId="0" fontId="27" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1284,6 +1288,792 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="F0F6FC"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="00C853"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI"/>
+              </a:rPr>
+              <a:t>Ausgaben nach Kategorie</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$C$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Betrag</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00C853"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00E676"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="69F0AE"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="58A6FF"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="56D4DD"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="BC8CFF"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="F778BA"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="E3B341"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="0D1117"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:separator> </c:separator>
+            <c:txPr>
+              <a:bodyPr rot="0" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="F0F6FC"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="de-DE"/>
+              </a:p>
+            </c:txPr>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$B$39:$B$46</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Lebensmittel</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Transport</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wohnung</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unterhaltung</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Gesundheit</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Bildung</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Kleidung</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Restaurant</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$C$39:$C$46</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00\ "\u20ac"</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr rot="0" vert="horz"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800">
+              <a:solidFill>
+                <a:srgbClr val="C9D1D9"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="161B22"/>
+    </a:solidFill>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="30363D"/>
+      </a:solidFill>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="00C853"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" sz="1400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="00C853"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI"/>
+              </a:rPr>
+              <a:t>Einnahmen vs. Ausgaben</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$C$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Einnahmen</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00C853"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$B$13:$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>M\u00e4r</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Mai</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Okt</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dez</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$C$13:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00\ "\u20ac"</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$D$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ausgaben</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F85149"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$B$13:$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>M\u00e4r</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Mai</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Okt</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dez</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$D$13:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00\ "\u20ac"</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:overlap val="0"/>
+        <c:axId val="111111111"/>
+        <c:axId val="222222222"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="111111111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="6350">
+            <a:solidFill>
+              <a:srgbClr val="30363D"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:srgbClr val="C9D1D9"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="222222222"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="222222222"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0\ &quot;\u20ac&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800">
+                <a:solidFill>
+                  <a:srgbClr val="8B949E"/>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="111111111"/>
+        <c:crosses val="autoZero"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="3175">
+              <a:solidFill>
+                <a:srgbClr val="21262D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr rot="0" vert="horz"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="C9D1D9"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="161B22"/>
+    </a:solidFill>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="30363D"/>
+      </a:solidFill>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Pie Chart"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Bar Chart"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1611,7 +2401,7 @@
   <sheetPr>
     <tabColor rgb="00C853"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1860,10 +2650,10 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="24">
-        <f>IF(Budgets!A3="","",Budgets!A3)</f>
+        <f>IF(Budgets!B4="","",Budgets!B4)</f>
       </c>
       <c r="I13" s="29">
-        <f>IF(H13="","",Budgets!B3)</f>
+        <f>IF(H13="","",Budgets!C4)</f>
       </c>
       <c r="J13" s="26">
         <f>IF(H13="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H13)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -1892,10 +2682,10 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="31">
-        <f>IF(Budgets!A4="","",Budgets!A4)</f>
+        <f>IF(Budgets!B5="","",Budgets!B5)</f>
       </c>
       <c r="I14" s="36">
-        <f>IF(H14="","",Budgets!B4)</f>
+        <f>IF(H14="","",Budgets!C5)</f>
       </c>
       <c r="J14" s="33">
         <f>IF(H14="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H14)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -1924,10 +2714,10 @@
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="24">
-        <f>IF(Budgets!A5="","",Budgets!A5)</f>
+        <f>IF(Budgets!B6="","",Budgets!B6)</f>
       </c>
       <c r="I15" s="29">
-        <f>IF(H15="","",Budgets!B5)</f>
+        <f>IF(H15="","",Budgets!C6)</f>
       </c>
       <c r="J15" s="26">
         <f>IF(H15="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H15)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -1956,10 +2746,10 @@
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="31">
-        <f>IF(Budgets!A6="","",Budgets!A6)</f>
+        <f>IF(Budgets!B7="","",Budgets!B7)</f>
       </c>
       <c r="I16" s="36">
-        <f>IF(H16="","",Budgets!B6)</f>
+        <f>IF(H16="","",Budgets!C7)</f>
       </c>
       <c r="J16" s="33">
         <f>IF(H16="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H16)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -1988,10 +2778,10 @@
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="24">
-        <f>IF(Budgets!A7="","",Budgets!A7)</f>
+        <f>IF(Budgets!B8="","",Budgets!B8)</f>
       </c>
       <c r="I17" s="29">
-        <f>IF(H17="","",Budgets!B7)</f>
+        <f>IF(H17="","",Budgets!C8)</f>
       </c>
       <c r="J17" s="26">
         <f>IF(H17="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H17)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -2020,10 +2810,10 @@
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="31">
-        <f>IF(Budgets!A8="","",Budgets!A8)</f>
+        <f>IF(Budgets!B9="","",Budgets!B9)</f>
       </c>
       <c r="I18" s="36">
-        <f>IF(H18="","",Budgets!B8)</f>
+        <f>IF(H18="","",Budgets!C9)</f>
       </c>
       <c r="J18" s="33">
         <f>IF(H18="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H18)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -2052,10 +2842,10 @@
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="24">
-        <f>IF(Budgets!A9="","",Budgets!A9)</f>
+        <f>IF(Budgets!B10="","",Budgets!B10)</f>
       </c>
       <c r="I19" s="29">
-        <f>IF(H19="","",Budgets!B9)</f>
+        <f>IF(H19="","",Budgets!C10)</f>
       </c>
       <c r="J19" s="26">
         <f>IF(H19="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H19)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -2084,10 +2874,10 @@
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="31">
-        <f>IF(Budgets!A10="","",Budgets!A10)</f>
+        <f>IF(Budgets!B11="","",Budgets!B11)</f>
       </c>
       <c r="I20" s="36">
-        <f>IF(H20="","",Budgets!B10)</f>
+        <f>IF(H20="","",Budgets!C11)</f>
       </c>
       <c r="J20" s="33">
         <f>IF(H20="","",SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!F$4:F$500=H20)*(MONTH(Transaktionen!C$4:C$500)=MONTH(TODAY()))*(YEAR(Transaktionen!C$4:C$500)=YEAR(TODAY()))*Transaktionen!E$4:E$500))</f>
@@ -2310,22 +3100,22 @@
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
       <c r="B30" s="24">
-        <f>IF(Konten!A3="","",Konten!A3)</f>
+        <f>IF(Konten!B4="","",Konten!B4)</f>
       </c>
       <c r="C30" s="43">
-        <f>IF(B30="","",Konten!B3)</f>
+        <f>IF(B30="","",Konten!C4)</f>
       </c>
       <c r="D30" s="29">
-        <f>IF(B30="","",Konten!C3)</f>
+        <f>IF(B30="","",Konten!D4)</f>
       </c>
       <c r="E30" s="25">
-        <f>IF(B30="","",Konten!D3)</f>
+        <f>IF(B30="","",Konten!E4)</f>
       </c>
       <c r="F30" s="26">
-        <f>IF(B30="","",Konten!E3)</f>
+        <f>IF(B30="","",Konten!F4)</f>
       </c>
       <c r="G30" s="44">
-        <f>IF(B30="","",Konten!F3)</f>
+        <f>IF(B30="","",Konten!G4)</f>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2336,22 +3126,22 @@
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="23"/>
       <c r="B31" s="31">
-        <f>IF(Konten!A4="","",Konten!A4)</f>
+        <f>IF(Konten!B5="","",Konten!B5)</f>
       </c>
       <c r="C31" s="45">
-        <f>IF(B31="","",Konten!B4)</f>
+        <f>IF(B31="","",Konten!C5)</f>
       </c>
       <c r="D31" s="36">
-        <f>IF(B31="","",Konten!C4)</f>
+        <f>IF(B31="","",Konten!D5)</f>
       </c>
       <c r="E31" s="32">
-        <f>IF(B31="","",Konten!D4)</f>
+        <f>IF(B31="","",Konten!E5)</f>
       </c>
       <c r="F31" s="33">
-        <f>IF(B31="","",Konten!E4)</f>
+        <f>IF(B31="","",Konten!F5)</f>
       </c>
       <c r="G31" s="46">
-        <f>IF(B31="","",Konten!F4)</f>
+        <f>IF(B31="","",Konten!G5)</f>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2362,22 +3152,22 @@
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="23"/>
       <c r="B32" s="24">
-        <f>IF(Konten!A5="","",Konten!A5)</f>
+        <f>IF(Konten!B6="","",Konten!B6)</f>
       </c>
       <c r="C32" s="43">
-        <f>IF(B32="","",Konten!B5)</f>
+        <f>IF(B32="","",Konten!C6)</f>
       </c>
       <c r="D32" s="29">
-        <f>IF(B32="","",Konten!C5)</f>
+        <f>IF(B32="","",Konten!D6)</f>
       </c>
       <c r="E32" s="25">
-        <f>IF(B32="","",Konten!D5)</f>
+        <f>IF(B32="","",Konten!E6)</f>
       </c>
       <c r="F32" s="26">
-        <f>IF(B32="","",Konten!E5)</f>
+        <f>IF(B32="","",Konten!F6)</f>
       </c>
       <c r="G32" s="44">
-        <f>IF(B32="","",Konten!F5)</f>
+        <f>IF(B32="","",Konten!G6)</f>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2388,22 +3178,22 @@
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
       <c r="B33" s="31">
-        <f>IF(Konten!A6="","",Konten!A6)</f>
+        <f>IF(Konten!B7="","",Konten!B7)</f>
       </c>
       <c r="C33" s="45">
-        <f>IF(B33="","",Konten!B6)</f>
+        <f>IF(B33="","",Konten!C7)</f>
       </c>
       <c r="D33" s="36">
-        <f>IF(B33="","",Konten!C6)</f>
+        <f>IF(B33="","",Konten!D7)</f>
       </c>
       <c r="E33" s="32">
-        <f>IF(B33="","",Konten!D6)</f>
+        <f>IF(B33="","",Konten!E7)</f>
       </c>
       <c r="F33" s="33">
-        <f>IF(B33="","",Konten!E6)</f>
+        <f>IF(B33="","",Konten!F7)</f>
       </c>
       <c r="G33" s="46">
-        <f>IF(B33="","",Konten!F6)</f>
+        <f>IF(B33="","",Konten!G7)</f>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2528,16 +3318,16 @@
       <c r="F39" s="47"/>
       <c r="G39" s="47"/>
       <c r="H39" s="48">
-        <f>IF(Transaktionen!A3="","",Transaktionen!A3)</f>
+        <f>IF(Transaktionen!B4="","",Transaktionen!B4)</f>
       </c>
       <c r="I39" s="49">
-        <f>IF(H39="","",Transaktionen!B3)</f>
+        <f>IF(H39="","",Transaktionen!C4)</f>
       </c>
       <c r="J39" s="50">
-        <f>IF(H39="","",Transaktionen!E3)</f>
+        <f>IF(H39="","",Transaktionen!E4)</f>
       </c>
       <c r="K39" s="51">
-        <f>IF(H39="","",Transaktionen!C3)</f>
+        <f>IF(H39="","",Transaktionen!D4)</f>
       </c>
       <c r="L39" s="1"/>
     </row>
@@ -2558,16 +3348,16 @@
       <c r="F40" s="52"/>
       <c r="G40" s="52"/>
       <c r="H40" s="53">
-        <f>IF(Transaktionen!A4="","",Transaktionen!A4)</f>
+        <f>IF(Transaktionen!B5="","",Transaktionen!B5)</f>
       </c>
       <c r="I40" s="54">
-        <f>IF(H40="","",Transaktionen!B4)</f>
+        <f>IF(H40="","",Transaktionen!C5)</f>
       </c>
       <c r="J40" s="55">
-        <f>IF(H40="","",Transaktionen!E4)</f>
+        <f>IF(H40="","",Transaktionen!E5)</f>
       </c>
       <c r="K40" s="56">
-        <f>IF(H40="","",Transaktionen!C4)</f>
+        <f>IF(H40="","",Transaktionen!D5)</f>
       </c>
       <c r="L40" s="1"/>
     </row>
@@ -2588,16 +3378,16 @@
       <c r="F41" s="47"/>
       <c r="G41" s="47"/>
       <c r="H41" s="48">
-        <f>IF(Transaktionen!A5="","",Transaktionen!A5)</f>
+        <f>IF(Transaktionen!B6="","",Transaktionen!B6)</f>
       </c>
       <c r="I41" s="49">
-        <f>IF(H41="","",Transaktionen!B5)</f>
+        <f>IF(H41="","",Transaktionen!C6)</f>
       </c>
       <c r="J41" s="50">
-        <f>IF(H41="","",Transaktionen!E5)</f>
+        <f>IF(H41="","",Transaktionen!E6)</f>
       </c>
       <c r="K41" s="51">
-        <f>IF(H41="","",Transaktionen!C5)</f>
+        <f>IF(H41="","",Transaktionen!D6)</f>
       </c>
       <c r="L41" s="1"/>
     </row>
@@ -2618,16 +3408,16 @@
       <c r="F42" s="52"/>
       <c r="G42" s="52"/>
       <c r="H42" s="53">
-        <f>IF(Transaktionen!A6="","",Transaktionen!A6)</f>
+        <f>IF(Transaktionen!B7="","",Transaktionen!B7)</f>
       </c>
       <c r="I42" s="54">
-        <f>IF(H42="","",Transaktionen!B6)</f>
+        <f>IF(H42="","",Transaktionen!C7)</f>
       </c>
       <c r="J42" s="55">
-        <f>IF(H42="","",Transaktionen!E6)</f>
+        <f>IF(H42="","",Transaktionen!E7)</f>
       </c>
       <c r="K42" s="56">
-        <f>IF(H42="","",Transaktionen!C6)</f>
+        <f>IF(H42="","",Transaktionen!D7)</f>
       </c>
       <c r="L42" s="1"/>
     </row>
@@ -2648,16 +3438,16 @@
       <c r="F43" s="47"/>
       <c r="G43" s="47"/>
       <c r="H43" s="48">
-        <f>IF(Transaktionen!A7="","",Transaktionen!A7)</f>
+        <f>IF(Transaktionen!B8="","",Transaktionen!B8)</f>
       </c>
       <c r="I43" s="49">
-        <f>IF(H43="","",Transaktionen!B7)</f>
+        <f>IF(H43="","",Transaktionen!C8)</f>
       </c>
       <c r="J43" s="50">
-        <f>IF(H43="","",Transaktionen!E7)</f>
+        <f>IF(H43="","",Transaktionen!E8)</f>
       </c>
       <c r="K43" s="51">
-        <f>IF(H43="","",Transaktionen!C7)</f>
+        <f>IF(H43="","",Transaktionen!D8)</f>
       </c>
       <c r="L43" s="1"/>
     </row>
@@ -2678,16 +3468,16 @@
       <c r="F44" s="52"/>
       <c r="G44" s="52"/>
       <c r="H44" s="53">
-        <f>IF(Transaktionen!A8="","",Transaktionen!A8)</f>
+        <f>IF(Transaktionen!B9="","",Transaktionen!B9)</f>
       </c>
       <c r="I44" s="54">
-        <f>IF(H44="","",Transaktionen!B8)</f>
+        <f>IF(H44="","",Transaktionen!C9)</f>
       </c>
       <c r="J44" s="55">
-        <f>IF(H44="","",Transaktionen!E8)</f>
+        <f>IF(H44="","",Transaktionen!E9)</f>
       </c>
       <c r="K44" s="56">
-        <f>IF(H44="","",Transaktionen!C8)</f>
+        <f>IF(H44="","",Transaktionen!D9)</f>
       </c>
       <c r="L44" s="1"/>
     </row>
@@ -2708,16 +3498,16 @@
       <c r="F45" s="47"/>
       <c r="G45" s="47"/>
       <c r="H45" s="48">
-        <f>IF(Transaktionen!A9="","",Transaktionen!A9)</f>
+        <f>IF(Transaktionen!B10="","",Transaktionen!B10)</f>
       </c>
       <c r="I45" s="49">
-        <f>IF(H45="","",Transaktionen!B9)</f>
+        <f>IF(H45="","",Transaktionen!C10)</f>
       </c>
       <c r="J45" s="50">
-        <f>IF(H45="","",Transaktionen!E9)</f>
+        <f>IF(H45="","",Transaktionen!E10)</f>
       </c>
       <c r="K45" s="51">
-        <f>IF(H45="","",Transaktionen!C9)</f>
+        <f>IF(H45="","",Transaktionen!D10)</f>
       </c>
       <c r="L45" s="1"/>
     </row>
@@ -2738,16 +3528,16 @@
       <c r="F46" s="52"/>
       <c r="G46" s="52"/>
       <c r="H46" s="53">
-        <f>IF(Transaktionen!A10="","",Transaktionen!A10)</f>
+        <f>IF(Transaktionen!B11="","",Transaktionen!B11)</f>
       </c>
       <c r="I46" s="54">
-        <f>IF(H46="","",Transaktionen!B10)</f>
+        <f>IF(H46="","",Transaktionen!C11)</f>
       </c>
       <c r="J46" s="55">
-        <f>IF(H46="","",Transaktionen!E10)</f>
+        <f>IF(H46="","",Transaktionen!E11)</f>
       </c>
       <c r="K46" s="56">
-        <f>IF(H46="","",Transaktionen!C10)</f>
+        <f>IF(H46="","",Transaktionen!D11)</f>
       </c>
       <c r="L46" s="1"/>
     </row>
@@ -2765,34 +3555,34 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="B48" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
       <c r="L48" s="1"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
-      <c r="K49" s="57"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2879,9 +3669,221 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
     </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="58"/>
+      <c r="K65" s="58"/>
+      <c r="L65" s="1"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="1"/>
-  <mergeCells count="37">
+  <mergeCells count="38">
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B4:K4"/>
@@ -2918,7 +3920,8 @@
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="E46:G46"/>
-    <mergeCell ref="B49:K49"/>
+    <mergeCell ref="B48:K48"/>
+    <mergeCell ref="B65:K65"/>
   </mergeCells>
   <conditionalFormatting sqref="K13:K20">
     <cfRule type="containsText" dxfId="0" priority="1">
@@ -2938,6 +3941,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2960,14 +3964,14 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" ht="4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3003,1176 +4007,1176 @@
         <v>32</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="49">
         <v>46054</v>
       </c>
-      <c r="D4" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="60">
+      <c r="D4" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="61">
         <v>3500</v>
       </c>
-      <c r="F4" s="61" t="s">
-        <v>50</v>
+      <c r="F4" s="62" t="s">
+        <v>51</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="62" t="s">
         <v>52</v>
+      </c>
+      <c r="H4" s="63" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="23"/>
       <c r="B5" s="53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="54">
         <v>46056</v>
       </c>
-      <c r="D5" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="63">
+      <c r="D5" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="64">
         <v>800</v>
       </c>
-      <c r="F5" s="64" t="s">
-        <v>54</v>
+      <c r="F5" s="65" t="s">
+        <v>55</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="65" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="49">
         <v>46054</v>
       </c>
-      <c r="D6" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="67">
+      <c r="D6" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="68">
         <v>950</v>
       </c>
-      <c r="F6" s="61" t="s">
-        <v>58</v>
+      <c r="F6" s="62" t="s">
+        <v>59</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="62" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="54">
         <v>46058</v>
       </c>
-      <c r="D7" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="68">
+      <c r="D7" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="69">
         <v>67.5</v>
       </c>
-      <c r="F7" s="64" t="s">
-        <v>61</v>
+      <c r="F7" s="65" t="s">
+        <v>62</v>
       </c>
       <c r="G7" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="65" t="s">
         <v>63</v>
+      </c>
+      <c r="H7" s="66" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="49">
         <v>46060</v>
       </c>
-      <c r="D8" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="67">
+      <c r="D8" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="68">
         <v>55</v>
       </c>
-      <c r="F8" s="61" t="s">
-        <v>65</v>
+      <c r="F8" s="62" t="s">
+        <v>66</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="62" t="s">
         <v>67</v>
+      </c>
+      <c r="H8" s="63" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="54">
         <v>46061</v>
       </c>
-      <c r="D9" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="68">
+      <c r="D9" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="69">
         <v>12.99</v>
       </c>
-      <c r="F9" s="64" t="s">
-        <v>69</v>
+      <c r="F9" s="65" t="s">
+        <v>70</v>
       </c>
       <c r="G9" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="65" t="s">
-        <v>70</v>
+        <v>52</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="49">
         <v>46063</v>
       </c>
-      <c r="D10" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="67">
+      <c r="D10" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="68">
         <v>30</v>
       </c>
-      <c r="F10" s="61" t="s">
-        <v>72</v>
+      <c r="F10" s="62" t="s">
+        <v>73</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="62" t="s">
-        <v>73</v>
+        <v>52</v>
+      </c>
+      <c r="H10" s="63" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" s="54">
         <v>46065</v>
       </c>
-      <c r="D11" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="68">
+      <c r="D11" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="69">
         <v>45.8</v>
       </c>
-      <c r="F11" s="64" t="s">
-        <v>75</v>
+      <c r="F11" s="65" t="s">
+        <v>76</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="65" t="s">
-        <v>76</v>
+        <v>67</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="49">
         <v>46067</v>
       </c>
-      <c r="D12" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="67">
+      <c r="D12" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="68">
         <v>29.99</v>
       </c>
-      <c r="F12" s="61" t="s">
-        <v>78</v>
+      <c r="F12" s="62" t="s">
+        <v>79</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="62" t="s">
-        <v>79</v>
+        <v>67</v>
+      </c>
+      <c r="H12" s="63" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="54">
         <v>46069</v>
       </c>
-      <c r="D13" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="68">
+      <c r="D13" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="69">
         <v>43.2</v>
       </c>
-      <c r="F13" s="64" t="s">
-        <v>61</v>
+      <c r="F13" s="65" t="s">
+        <v>62</v>
       </c>
       <c r="G13" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="65" t="s">
         <v>63</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="48" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" s="49">
         <v>46071</v>
       </c>
-      <c r="D14" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="67">
+      <c r="D14" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="68">
         <v>25</v>
       </c>
-      <c r="F14" s="61" t="s">
-        <v>82</v>
+      <c r="F14" s="62" t="s">
+        <v>83</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="62" t="s">
-        <v>83</v>
+        <v>67</v>
+      </c>
+      <c r="H14" s="63" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="23"/>
       <c r="B15" s="53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" s="54">
         <v>46073</v>
       </c>
-      <c r="D15" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="63">
+      <c r="D15" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="64">
         <v>120</v>
       </c>
-      <c r="F15" s="64" t="s">
-        <v>85</v>
+      <c r="F15" s="65" t="s">
+        <v>86</v>
       </c>
       <c r="G15" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="65" t="s">
         <v>87</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="23"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="61"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="29"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="64"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="65"/>
       <c r="E17" s="36"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="61"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="29"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="65"/>
       <c r="E19" s="36"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="61"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="29"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="36"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="23"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="61"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="29"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="23"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="64"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="36"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="23"/>
-      <c r="B24" s="61"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="61"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="29"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="64"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="65"/>
       <c r="E25" s="36"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="64"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="23"/>
-      <c r="B26" s="61"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="61"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="29"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="23"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="64"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="65"/>
       <c r="E27" s="36"/>
-      <c r="F27" s="64"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="64"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
-      <c r="B28" s="61"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="61"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="29"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="23"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="64"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="65"/>
       <c r="E29" s="36"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
-      <c r="B30" s="61"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="61"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="29"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="23"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="64"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="65"/>
       <c r="E31" s="36"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="23"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="29"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="64"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="65"/>
       <c r="E33" s="36"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="61"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="29"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="64"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="65"/>
       <c r="E35" s="36"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="61"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="62"/>
       <c r="E36" s="29"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="64"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="65"/>
       <c r="E37" s="36"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="61"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="62"/>
       <c r="E38" s="29"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="62"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="64"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="65"/>
       <c r="E39" s="36"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="61"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="62"/>
       <c r="E40" s="29"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
-      <c r="B41" s="64"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="64"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="65"/>
       <c r="E41" s="36"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="61"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="62"/>
       <c r="E42" s="29"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="64"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="64"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="65"/>
       <c r="E43" s="36"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="61"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="61"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="62"/>
       <c r="E44" s="29"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="62"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="64"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="64"/>
+      <c r="B45" s="65"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="65"/>
       <c r="E45" s="36"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="61"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="61"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="62"/>
       <c r="E46" s="29"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="62"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="64"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="64"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="65"/>
       <c r="E47" s="36"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="64"/>
-      <c r="H47" s="64"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="69"/>
-      <c r="D48" s="61"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="62"/>
       <c r="E48" s="29"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="62"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="64"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="64"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="65"/>
       <c r="E49" s="36"/>
-      <c r="F49" s="64"/>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="65"/>
+      <c r="H49" s="65"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="69"/>
-      <c r="D50" s="61"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="62"/>
       <c r="E50" s="29"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="64"/>
+      <c r="B51" s="65"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="65"/>
       <c r="E51" s="36"/>
-      <c r="F51" s="64"/>
-      <c r="G51" s="64"/>
-      <c r="H51" s="64"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="61"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="62"/>
       <c r="E52" s="29"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
+      <c r="F52" s="62"/>
+      <c r="G52" s="62"/>
+      <c r="H52" s="62"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="64"/>
+      <c r="B53" s="65"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="65"/>
       <c r="E53" s="36"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
+      <c r="F53" s="65"/>
+      <c r="G53" s="65"/>
+      <c r="H53" s="65"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="61"/>
-      <c r="C54" s="69"/>
-      <c r="D54" s="61"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="62"/>
       <c r="E54" s="29"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="61"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="62"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="64"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="64"/>
+      <c r="B55" s="65"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="65"/>
       <c r="E55" s="36"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="61"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="61"/>
+      <c r="B56" s="62"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="62"/>
       <c r="E56" s="29"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="64"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="64"/>
+      <c r="B57" s="65"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="65"/>
       <c r="E57" s="36"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="61"/>
+      <c r="B58" s="62"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="62"/>
       <c r="E58" s="29"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="61"/>
+      <c r="F58" s="62"/>
+      <c r="G58" s="62"/>
+      <c r="H58" s="62"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="64"/>
-      <c r="C59" s="70"/>
-      <c r="D59" s="64"/>
+      <c r="B59" s="65"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="65"/>
       <c r="E59" s="36"/>
-      <c r="F59" s="64"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="64"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="61"/>
-      <c r="C60" s="69"/>
-      <c r="D60" s="61"/>
+      <c r="B60" s="62"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="62"/>
       <c r="E60" s="29"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="62"/>
+      <c r="H60" s="62"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="64"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="64"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="65"/>
       <c r="E61" s="36"/>
-      <c r="F61" s="64"/>
-      <c r="G61" s="64"/>
-      <c r="H61" s="64"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="61"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="61"/>
+      <c r="B62" s="62"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="62"/>
       <c r="E62" s="29"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
+      <c r="F62" s="62"/>
+      <c r="G62" s="62"/>
+      <c r="H62" s="62"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="64"/>
-      <c r="C63" s="70"/>
-      <c r="D63" s="64"/>
+      <c r="B63" s="65"/>
+      <c r="C63" s="71"/>
+      <c r="D63" s="65"/>
       <c r="E63" s="36"/>
-      <c r="F63" s="64"/>
-      <c r="G63" s="64"/>
-      <c r="H63" s="64"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="65"/>
+      <c r="H63" s="65"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="61"/>
-      <c r="C64" s="69"/>
-      <c r="D64" s="61"/>
+      <c r="B64" s="62"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="62"/>
       <c r="E64" s="29"/>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="61"/>
+      <c r="F64" s="62"/>
+      <c r="G64" s="62"/>
+      <c r="H64" s="62"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="64"/>
-      <c r="C65" s="70"/>
-      <c r="D65" s="64"/>
+      <c r="B65" s="65"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="65"/>
       <c r="E65" s="36"/>
-      <c r="F65" s="64"/>
-      <c r="G65" s="64"/>
-      <c r="H65" s="64"/>
+      <c r="F65" s="65"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="65"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="61"/>
-      <c r="C66" s="69"/>
-      <c r="D66" s="61"/>
+      <c r="B66" s="62"/>
+      <c r="C66" s="70"/>
+      <c r="D66" s="62"/>
       <c r="E66" s="29"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61"/>
+      <c r="F66" s="62"/>
+      <c r="G66" s="62"/>
+      <c r="H66" s="62"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="64"/>
-      <c r="C67" s="70"/>
-      <c r="D67" s="64"/>
+      <c r="B67" s="65"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="65"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="64"/>
-      <c r="G67" s="64"/>
-      <c r="H67" s="64"/>
+      <c r="F67" s="65"/>
+      <c r="G67" s="65"/>
+      <c r="H67" s="65"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="61"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="61"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="62"/>
       <c r="E68" s="29"/>
-      <c r="F68" s="61"/>
-      <c r="G68" s="61"/>
-      <c r="H68" s="61"/>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="64"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="64"/>
+      <c r="B69" s="65"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="65"/>
       <c r="E69" s="36"/>
-      <c r="F69" s="64"/>
-      <c r="G69" s="64"/>
-      <c r="H69" s="64"/>
+      <c r="F69" s="65"/>
+      <c r="G69" s="65"/>
+      <c r="H69" s="65"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="61"/>
-      <c r="C70" s="69"/>
-      <c r="D70" s="61"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="62"/>
       <c r="E70" s="29"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="61"/>
-      <c r="H70" s="61"/>
+      <c r="F70" s="62"/>
+      <c r="G70" s="62"/>
+      <c r="H70" s="62"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="64"/>
-      <c r="C71" s="70"/>
-      <c r="D71" s="64"/>
+      <c r="B71" s="65"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="65"/>
       <c r="E71" s="36"/>
-      <c r="F71" s="64"/>
-      <c r="G71" s="64"/>
-      <c r="H71" s="64"/>
+      <c r="F71" s="65"/>
+      <c r="G71" s="65"/>
+      <c r="H71" s="65"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="69"/>
-      <c r="D72" s="61"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="62"/>
       <c r="E72" s="29"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
+      <c r="F72" s="62"/>
+      <c r="G72" s="62"/>
+      <c r="H72" s="62"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="64"/>
-      <c r="C73" s="70"/>
-      <c r="D73" s="64"/>
+      <c r="B73" s="65"/>
+      <c r="C73" s="71"/>
+      <c r="D73" s="65"/>
       <c r="E73" s="36"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="64"/>
-      <c r="H73" s="64"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="65"/>
+      <c r="H73" s="65"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="69"/>
-      <c r="D74" s="61"/>
+      <c r="B74" s="62"/>
+      <c r="C74" s="70"/>
+      <c r="D74" s="62"/>
       <c r="E74" s="29"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
+      <c r="F74" s="62"/>
+      <c r="G74" s="62"/>
+      <c r="H74" s="62"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="64"/>
-      <c r="C75" s="70"/>
-      <c r="D75" s="64"/>
+      <c r="B75" s="65"/>
+      <c r="C75" s="71"/>
+      <c r="D75" s="65"/>
       <c r="E75" s="36"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="64"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="69"/>
-      <c r="D76" s="61"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="62"/>
       <c r="E76" s="29"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
+      <c r="F76" s="62"/>
+      <c r="G76" s="62"/>
+      <c r="H76" s="62"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="64"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="64"/>
+      <c r="B77" s="65"/>
+      <c r="C77" s="71"/>
+      <c r="D77" s="65"/>
       <c r="E77" s="36"/>
-      <c r="F77" s="64"/>
-      <c r="G77" s="64"/>
-      <c r="H77" s="64"/>
+      <c r="F77" s="65"/>
+      <c r="G77" s="65"/>
+      <c r="H77" s="65"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="69"/>
-      <c r="D78" s="61"/>
+      <c r="B78" s="62"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="62"/>
       <c r="E78" s="29"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
+      <c r="F78" s="62"/>
+      <c r="G78" s="62"/>
+      <c r="H78" s="62"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="64"/>
-      <c r="C79" s="70"/>
-      <c r="D79" s="64"/>
+      <c r="B79" s="65"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="65"/>
       <c r="E79" s="36"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="64"/>
-      <c r="H79" s="64"/>
+      <c r="F79" s="65"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="65"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="61"/>
+      <c r="B80" s="62"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="62"/>
       <c r="E80" s="29"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
+      <c r="F80" s="62"/>
+      <c r="G80" s="62"/>
+      <c r="H80" s="62"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="64"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="64"/>
+      <c r="B81" s="65"/>
+      <c r="C81" s="71"/>
+      <c r="D81" s="65"/>
       <c r="E81" s="36"/>
-      <c r="F81" s="64"/>
-      <c r="G81" s="64"/>
-      <c r="H81" s="64"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="61"/>
+      <c r="B82" s="62"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="62"/>
       <c r="E82" s="29"/>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
+      <c r="F82" s="62"/>
+      <c r="G82" s="62"/>
+      <c r="H82" s="62"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="64"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="64"/>
+      <c r="B83" s="65"/>
+      <c r="C83" s="71"/>
+      <c r="D83" s="65"/>
       <c r="E83" s="36"/>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64"/>
-      <c r="H83" s="64"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="69"/>
-      <c r="D84" s="61"/>
+      <c r="B84" s="62"/>
+      <c r="C84" s="70"/>
+      <c r="D84" s="62"/>
       <c r="E84" s="29"/>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="70"/>
-      <c r="D85" s="64"/>
+      <c r="B85" s="65"/>
+      <c r="C85" s="71"/>
+      <c r="D85" s="65"/>
       <c r="E85" s="36"/>
-      <c r="F85" s="64"/>
-      <c r="G85" s="64"/>
-      <c r="H85" s="64"/>
+      <c r="F85" s="65"/>
+      <c r="G85" s="65"/>
+      <c r="H85" s="65"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="61"/>
-      <c r="C86" s="69"/>
-      <c r="D86" s="61"/>
+      <c r="B86" s="62"/>
+      <c r="C86" s="70"/>
+      <c r="D86" s="62"/>
       <c r="E86" s="29"/>
-      <c r="F86" s="61"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="61"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="62"/>
+      <c r="H86" s="62"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="64"/>
-      <c r="C87" s="70"/>
-      <c r="D87" s="64"/>
+      <c r="B87" s="65"/>
+      <c r="C87" s="71"/>
+      <c r="D87" s="65"/>
       <c r="E87" s="36"/>
-      <c r="F87" s="64"/>
-      <c r="G87" s="64"/>
-      <c r="H87" s="64"/>
+      <c r="F87" s="65"/>
+      <c r="G87" s="65"/>
+      <c r="H87" s="65"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="61"/>
-      <c r="C88" s="69"/>
-      <c r="D88" s="61"/>
+      <c r="B88" s="62"/>
+      <c r="C88" s="70"/>
+      <c r="D88" s="62"/>
       <c r="E88" s="29"/>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
+      <c r="F88" s="62"/>
+      <c r="G88" s="62"/>
+      <c r="H88" s="62"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="64"/>
-      <c r="C89" s="70"/>
-      <c r="D89" s="64"/>
+      <c r="B89" s="65"/>
+      <c r="C89" s="71"/>
+      <c r="D89" s="65"/>
       <c r="E89" s="36"/>
-      <c r="F89" s="64"/>
-      <c r="G89" s="64"/>
-      <c r="H89" s="64"/>
+      <c r="F89" s="65"/>
+      <c r="G89" s="65"/>
+      <c r="H89" s="65"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="69"/>
-      <c r="D90" s="61"/>
+      <c r="B90" s="62"/>
+      <c r="C90" s="70"/>
+      <c r="D90" s="62"/>
       <c r="E90" s="29"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
+      <c r="F90" s="62"/>
+      <c r="G90" s="62"/>
+      <c r="H90" s="62"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="64"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="64"/>
+      <c r="B91" s="65"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="65"/>
       <c r="E91" s="36"/>
-      <c r="F91" s="64"/>
-      <c r="G91" s="64"/>
-      <c r="H91" s="64"/>
+      <c r="F91" s="65"/>
+      <c r="G91" s="65"/>
+      <c r="H91" s="65"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="61"/>
+      <c r="B92" s="62"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="62"/>
       <c r="E92" s="29"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="61"/>
-      <c r="H92" s="61"/>
+      <c r="F92" s="62"/>
+      <c r="G92" s="62"/>
+      <c r="H92" s="62"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="64"/>
-      <c r="C93" s="70"/>
-      <c r="D93" s="64"/>
+      <c r="B93" s="65"/>
+      <c r="C93" s="71"/>
+      <c r="D93" s="65"/>
       <c r="E93" s="36"/>
-      <c r="F93" s="64"/>
-      <c r="G93" s="64"/>
-      <c r="H93" s="64"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="65"/>
+      <c r="H93" s="65"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="69"/>
-      <c r="D94" s="61"/>
+      <c r="B94" s="62"/>
+      <c r="C94" s="70"/>
+      <c r="D94" s="62"/>
       <c r="E94" s="29"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
+      <c r="F94" s="62"/>
+      <c r="G94" s="62"/>
+      <c r="H94" s="62"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="64"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="64"/>
+      <c r="B95" s="65"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="65"/>
       <c r="E95" s="36"/>
-      <c r="F95" s="64"/>
-      <c r="G95" s="64"/>
-      <c r="H95" s="64"/>
+      <c r="F95" s="65"/>
+      <c r="G95" s="65"/>
+      <c r="H95" s="65"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="69"/>
-      <c r="D96" s="61"/>
+      <c r="B96" s="62"/>
+      <c r="C96" s="70"/>
+      <c r="D96" s="62"/>
       <c r="E96" s="29"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="61"/>
+      <c r="F96" s="62"/>
+      <c r="G96" s="62"/>
+      <c r="H96" s="62"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="70"/>
-      <c r="D97" s="64"/>
+      <c r="B97" s="65"/>
+      <c r="C97" s="71"/>
+      <c r="D97" s="65"/>
       <c r="E97" s="36"/>
-      <c r="F97" s="64"/>
-      <c r="G97" s="64"/>
-      <c r="H97" s="64"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="65"/>
+      <c r="H97" s="65"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="61"/>
-      <c r="C98" s="69"/>
-      <c r="D98" s="61"/>
+      <c r="B98" s="62"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="62"/>
       <c r="E98" s="29"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="62"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="64"/>
-      <c r="C99" s="70"/>
-      <c r="D99" s="64"/>
+      <c r="B99" s="65"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="65"/>
       <c r="E99" s="36"/>
-      <c r="F99" s="64"/>
-      <c r="G99" s="64"/>
-      <c r="H99" s="64"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="61"/>
-      <c r="C100" s="69"/>
-      <c r="D100" s="61"/>
+      <c r="B100" s="62"/>
+      <c r="C100" s="70"/>
+      <c r="D100" s="62"/>
       <c r="E100" s="29"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="61"/>
+      <c r="F100" s="62"/>
+      <c r="G100" s="62"/>
+      <c r="H100" s="62"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="64"/>
-      <c r="C101" s="70"/>
-      <c r="D101" s="64"/>
+      <c r="B101" s="65"/>
+      <c r="C101" s="71"/>
+      <c r="D101" s="65"/>
       <c r="E101" s="36"/>
-      <c r="F101" s="64"/>
-      <c r="G101" s="64"/>
-      <c r="H101" s="64"/>
+      <c r="F101" s="65"/>
+      <c r="G101" s="65"/>
+      <c r="H101" s="65"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="61"/>
-      <c r="C102" s="69"/>
-      <c r="D102" s="61"/>
+      <c r="B102" s="62"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="62"/>
       <c r="E102" s="29"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="61"/>
+      <c r="F102" s="62"/>
+      <c r="G102" s="62"/>
+      <c r="H102" s="62"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="64"/>
-      <c r="C103" s="70"/>
-      <c r="D103" s="64"/>
+      <c r="B103" s="65"/>
+      <c r="C103" s="71"/>
+      <c r="D103" s="65"/>
       <c r="E103" s="36"/>
-      <c r="F103" s="64"/>
-      <c r="G103" s="64"/>
-      <c r="H103" s="64"/>
+      <c r="F103" s="65"/>
+      <c r="G103" s="65"/>
+      <c r="H103" s="65"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
@@ -4258,24 +5262,50 @@
       <formula>NOT(ISERROR(SEARCH("Ausgabe",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="D10:D103">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Beschreibung" prompt="Aus Liste wählen oder frei eintippen" sqref="B10:B103">
+      <formula1>"Miete,Gehalt,Einkauf REWE,Einkauf LIDL,Einkauf ALDI,Tankstelle,Netflix,Spotify,Restaurant,Arztbesuch,Apotheke,Strom,Internet,Handyvertrag,Versicherung,Freelance,Dividende,Online Kurs,Kleidung,Geschenk"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Beschreibung" prompt="Aus Liste wählen oder frei eintippen" sqref="B4:B103">
+      <formula1>"Miete,Gehalt,Einkauf REWE,Einkauf LIDL,Einkauf ALDI,Tankstelle,Netflix,Spotify,Restaurant,Arztbesuch,Apotheke,Strom,Internet,Handyvertrag,Versicherung,Freelance,Dividende,Online Kurs,Kleidung,Geschenk"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" promptTitle="Datum" prompt="Format: TT.MM.JJJJ" showErrorMessage="1" errorTitle="Ungültiges Datum" error="Bitte ein gültiges Datum eingeben" sqref="C10:C103">
+      <formula1>43831</formula1>
+      <formula2>47848</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" promptTitle="Datum" prompt="Format: TT.MM.JJJJ" showErrorMessage="1" errorTitle="Ungültiges Datum" error="Bitte ein gültiges Datum eingeben" sqref="C4:C103">
+      <formula1>43831</formula1>
+      <formula2>47848</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Typ wählen" prompt="Einnahme oder Ausgabe" showErrorMessage="1" errorTitle="Ungültiger Typ" error="Bitte Einnahme oder Ausgabe wählen" sqref="D10:D103">
       <formula1>"Einnahme,Ausgabe"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D4:D103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Typ wählen" prompt="Einnahme oder Ausgabe" showErrorMessage="1" errorTitle="Ungültiger Typ" error="Bitte Einnahme oder Ausgabe wählen" sqref="D4:D103">
       <formula1>"Einnahme,Ausgabe"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F10:F103">
-      <formula1>Kategorien!$A$4:$A$20</formula1>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" promptTitle="Betrag" prompt="Betrag in Euro eingeben (z.B. 49.99)" showErrorMessage="1" errorTitle="Ungültiger Betrag" error="Bitte einen positiven Betrag eingeben" sqref="E10:E103">
+      <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F4:F103">
-      <formula1>Kategorien!$A$4:$A$20</formula1>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" promptTitle="Betrag" prompt="Betrag in Euro eingeben (z.B. 49.99)" showErrorMessage="1" errorTitle="Ungültiger Betrag" error="Bitte einen positiven Betrag eingeben" sqref="E4:E103">
+      <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Kategorie" prompt="Kategorie aus der Liste wählen" showErrorMessage="1" errorTitle="Ungültige Kategorie" error="Bitte eine Kategorie aus der Liste wählen" sqref="F10:F103">
+      <formula1>Kategorien!$B$4:$B$20</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Kategorie" prompt="Kategorie aus der Liste wählen" showErrorMessage="1" errorTitle="Ungültige Kategorie" error="Bitte eine Kategorie aus der Liste wählen" sqref="F4:F103">
+      <formula1>Kategorien!$B$4:$B$20</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Konto" prompt="Konto aus der Liste wählen" showErrorMessage="1" errorTitle="Ungültiges Konto" error="Bitte ein Konto aus der Liste wählen" sqref="G10:G103">
       <formula1>Konten!$B$4:$B$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G4:G103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Konto" prompt="Konto aus der Liste wählen" showErrorMessage="1" errorTitle="Ungültiges Konto" error="Bitte ein Konto aus der Liste wählen" sqref="G4:G103">
       <formula1>Konten!$B$4:$B$12</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Notizen" prompt="Optionale Notizen zur Transaktion" sqref="H10:H103">
+      <formula1>500</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Notizen" prompt="Optionale Notizen zur Transaktion" sqref="H4:H103">
+      <formula1>500</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4301,12 +5331,12 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" ht="4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4328,10 +5358,10 @@
         <v>33</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>11</v>
@@ -4340,225 +5370,225 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="60" t="s">
         <v>50</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>49</v>
       </c>
       <c r="D4" s="29">
         <v>0</v>
       </c>
-      <c r="E4" s="71" t="s">
-        <v>91</v>
+      <c r="E4" s="72" t="s">
+        <v>92</v>
       </c>
       <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="23"/>
       <c r="B5" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>50</v>
       </c>
       <c r="D5" s="36">
         <v>0</v>
       </c>
-      <c r="E5" s="72" t="s">
-        <v>92</v>
+      <c r="E5" s="73" t="s">
+        <v>93</v>
       </c>
       <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>49</v>
+        <v>86</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>50</v>
       </c>
       <c r="D6" s="29">
         <v>0</v>
       </c>
-      <c r="E6" s="71" t="s">
-        <v>93</v>
+      <c r="E6" s="72" t="s">
+        <v>94</v>
       </c>
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>49</v>
+        <v>95</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>50</v>
       </c>
       <c r="D7" s="36">
         <v>0</v>
       </c>
-      <c r="E7" s="72" t="s">
-        <v>95</v>
+      <c r="E7" s="73" t="s">
+        <v>96</v>
       </c>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D8" s="29">
         <v>400</v>
       </c>
-      <c r="E8" s="71" t="s">
-        <v>96</v>
+      <c r="E8" s="72" t="s">
+        <v>97</v>
       </c>
       <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="66" t="s">
-        <v>57</v>
+        <v>66</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D9" s="36">
         <v>150</v>
       </c>
-      <c r="E9" s="72" t="s">
-        <v>97</v>
+      <c r="E9" s="73" t="s">
+        <v>98</v>
       </c>
       <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="67" t="s">
         <v>58</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>57</v>
       </c>
       <c r="D10" s="29">
         <v>1000</v>
       </c>
-      <c r="E10" s="71" t="s">
-        <v>98</v>
+      <c r="E10" s="72" t="s">
+        <v>99</v>
       </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="66" t="s">
-        <v>57</v>
+        <v>70</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D11" s="36">
         <v>100</v>
       </c>
-      <c r="E11" s="72" t="s">
-        <v>99</v>
+      <c r="E11" s="73" t="s">
+        <v>100</v>
       </c>
       <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>57</v>
+        <v>73</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D12" s="29">
         <v>50</v>
       </c>
-      <c r="E12" s="71" t="s">
-        <v>100</v>
+      <c r="E12" s="72" t="s">
+        <v>101</v>
       </c>
       <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="66" t="s">
-        <v>57</v>
+        <v>79</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D13" s="36">
         <v>50</v>
       </c>
-      <c r="E13" s="72" t="s">
-        <v>101</v>
+      <c r="E13" s="73" t="s">
+        <v>102</v>
       </c>
       <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="23"/>
       <c r="B14" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>57</v>
+        <v>83</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D14" s="29">
         <v>80</v>
       </c>
-      <c r="E14" s="71" t="s">
-        <v>102</v>
+      <c r="E14" s="72" t="s">
+        <v>103</v>
       </c>
       <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="23"/>
       <c r="B15" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="66" t="s">
-        <v>57</v>
+        <v>76</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>58</v>
       </c>
       <c r="D15" s="36">
         <v>100</v>
       </c>
-      <c r="E15" s="72" t="s">
-        <v>93</v>
+      <c r="E15" s="73" t="s">
+        <v>94</v>
       </c>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="23"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="29"/>
-      <c r="E16" s="61"/>
+      <c r="E16" s="62"/>
       <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
       <c r="D17" s="36"/>
-      <c r="E17" s="64"/>
+      <c r="E17" s="65"/>
       <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
       <c r="D18" s="29"/>
-      <c r="E18" s="61"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="36"/>
-      <c r="E19" s="64"/>
+      <c r="E19" s="65"/>
       <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,15 +5716,15 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" ht="4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4722,16 +5752,16 @@
         <v>14</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>11</v>
@@ -4740,7 +5770,7 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="29">
         <v>400</v>
@@ -4751,13 +5781,13 @@
       <c r="E4" s="27">
         <f>C4-D4</f>
       </c>
-      <c r="F4" s="73">
+      <c r="F4" s="74">
         <f>IF(C4=0,0,D4/C4)</f>
       </c>
-      <c r="G4" s="74">
+      <c r="G4" s="75">
         <f>IF(C4=0,"—",IF(F4&gt;1,"OVER",IF(F4&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="76">
         <f>IF(C4=0,"",REPT("█",MIN(ROUND(F4*20,0),20))&amp;REPT("░",MAX(20-ROUND(F4*20,0),0)))</f>
       </c>
       <c r="I4" s="23"/>
@@ -4765,7 +5795,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="23"/>
       <c r="B5" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="36">
         <v>150</v>
@@ -4776,13 +5806,13 @@
       <c r="E5" s="34">
         <f>C5-D5</f>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="77">
         <f>IF(C5=0,0,D5/C5)</f>
       </c>
-      <c r="G5" s="77">
+      <c r="G5" s="78">
         <f>IF(C5=0,"—",IF(F5&gt;1,"OVER",IF(F5&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H5" s="78">
+      <c r="H5" s="79">
         <f>IF(C5=0,"",REPT("█",MIN(ROUND(F5*20,0),20))&amp;REPT("░",MAX(20-ROUND(F5*20,0),0)))</f>
       </c>
       <c r="I5" s="23"/>
@@ -4790,7 +5820,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="29">
         <v>1000</v>
@@ -4801,13 +5831,13 @@
       <c r="E6" s="27">
         <f>C6-D6</f>
       </c>
-      <c r="F6" s="73">
+      <c r="F6" s="74">
         <f>IF(C6=0,0,D6/C6)</f>
       </c>
-      <c r="G6" s="74">
+      <c r="G6" s="75">
         <f>IF(C6=0,"—",IF(F6&gt;1,"OVER",IF(F6&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="76">
         <f>IF(C6=0,"",REPT("█",MIN(ROUND(F6*20,0),20))&amp;REPT("░",MAX(20-ROUND(F6*20,0),0)))</f>
       </c>
       <c r="I6" s="23"/>
@@ -4815,7 +5845,7 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="36">
         <v>100</v>
@@ -4826,13 +5856,13 @@
       <c r="E7" s="34">
         <f>C7-D7</f>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="77">
         <f>IF(C7=0,0,D7/C7)</f>
       </c>
-      <c r="G7" s="77">
+      <c r="G7" s="78">
         <f>IF(C7=0,"—",IF(F7&gt;1,"OVER",IF(F7&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H7" s="78">
+      <c r="H7" s="79">
         <f>IF(C7=0,"",REPT("█",MIN(ROUND(F7*20,0),20))&amp;REPT("░",MAX(20-ROUND(F7*20,0),0)))</f>
       </c>
       <c r="I7" s="23"/>
@@ -4840,7 +5870,7 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="29">
         <v>50</v>
@@ -4851,13 +5881,13 @@
       <c r="E8" s="27">
         <f>C8-D8</f>
       </c>
-      <c r="F8" s="73">
+      <c r="F8" s="74">
         <f>IF(C8=0,0,D8/C8)</f>
       </c>
-      <c r="G8" s="74">
+      <c r="G8" s="75">
         <f>IF(C8=0,"—",IF(F8&gt;1,"OVER",IF(F8&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="76">
         <f>IF(C8=0,"",REPT("█",MIN(ROUND(F8*20,0),20))&amp;REPT("░",MAX(20-ROUND(F8*20,0),0)))</f>
       </c>
       <c r="I8" s="23"/>
@@ -4865,7 +5895,7 @@
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" s="36">
         <v>50</v>
@@ -4876,13 +5906,13 @@
       <c r="E9" s="34">
         <f>C9-D9</f>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="77">
         <f>IF(C9=0,0,D9/C9)</f>
       </c>
-      <c r="G9" s="77">
+      <c r="G9" s="78">
         <f>IF(C9=0,"—",IF(F9&gt;1,"OVER",IF(F9&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="79">
         <f>IF(C9=0,"",REPT("█",MIN(ROUND(F9*20,0),20))&amp;REPT("░",MAX(20-ROUND(F9*20,0),0)))</f>
       </c>
       <c r="I9" s="23"/>
@@ -4890,7 +5920,7 @@
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="29">
         <v>80</v>
@@ -4901,13 +5931,13 @@
       <c r="E10" s="27">
         <f>C10-D10</f>
       </c>
-      <c r="F10" s="73">
+      <c r="F10" s="74">
         <f>IF(C10=0,0,D10/C10)</f>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="75">
         <f>IF(C10=0,"—",IF(F10&gt;1,"OVER",IF(F10&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H10" s="75">
+      <c r="H10" s="76">
         <f>IF(C10=0,"",REPT("█",MIN(ROUND(F10*20,0),20))&amp;REPT("░",MAX(20-ROUND(F10*20,0),0)))</f>
       </c>
       <c r="I10" s="23"/>
@@ -4915,7 +5945,7 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="36">
         <v>100</v>
@@ -4926,13 +5956,13 @@
       <c r="E11" s="34">
         <f>C11-D11</f>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="77">
         <f>IF(C11=0,0,D11/C11)</f>
       </c>
-      <c r="G11" s="77">
+      <c r="G11" s="78">
         <f>IF(C11=0,"—",IF(F11&gt;1,"OVER",IF(F11&gt;0.8,"WARN","OK")))</f>
       </c>
-      <c r="H11" s="78">
+      <c r="H11" s="79">
         <f>IF(C11=0,"",REPT("█",MIN(ROUND(F11*20,0),20))&amp;REPT("░",MAX(20-ROUND(F11*20,0),0)))</f>
       </c>
       <c r="I11" s="23"/>
@@ -5153,14 +6183,14 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" ht="4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5178,7 +6208,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>33</v>
@@ -5202,10 +6232,10 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="79" t="s">
-        <v>109</v>
+        <v>52</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>110</v>
       </c>
       <c r="D4" s="29">
         <v>2500</v>
@@ -5216,7 +6246,7 @@
       <c r="F4" s="26">
         <f>SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!G$4:G$500=B4)*Transaktionen!E$4:E$500)</f>
       </c>
-      <c r="G4" s="80">
+      <c r="G4" s="81">
         <f>D4+E4-F4</f>
       </c>
       <c r="H4" s="23"/>
@@ -5224,10 +6254,10 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="23"/>
       <c r="B5" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="81" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="C5" s="82" t="s">
+        <v>63</v>
       </c>
       <c r="D5" s="36">
         <v>200</v>
@@ -5238,7 +6268,7 @@
       <c r="F5" s="33">
         <f>SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!G$4:G$500=B5)*Transaktionen!E$4:E$500)</f>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="83">
         <f>D5+E5-F5</f>
       </c>
       <c r="H5" s="23"/>
@@ -5246,10 +6276,10 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="79" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>67</v>
       </c>
       <c r="D6" s="29">
         <v>0</v>
@@ -5260,7 +6290,7 @@
       <c r="F6" s="26">
         <f>SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!G$4:G$500=B6)*Transaktionen!E$4:E$500)</f>
       </c>
-      <c r="G6" s="80">
+      <c r="G6" s="81">
         <f>D6+E6-F6</f>
       </c>
       <c r="H6" s="23"/>
@@ -5268,10 +6298,10 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="81" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>87</v>
       </c>
       <c r="D7" s="36">
         <v>5000</v>
@@ -5282,15 +6312,15 @@
       <c r="F7" s="33">
         <f>SUMPRODUCT((Transaktionen!D$4:D$500="Ausgabe")*(Transaktionen!G$4:G$500=B7)*Transaktionen!E$4:E$500)</f>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="83">
         <f>D7+E7-F7</f>
       </c>
       <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="29"/>
       <c r="E8" s="29">
         <f>IF(B8="","",SUMPRODUCT((Transaktionen!D$4:D$500="Einnahme")*(Transaktionen!G$4:G$500=B8)*Transaktionen!E$4:E$500))</f>
@@ -5305,8 +6335,8 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
       <c r="D9" s="36"/>
       <c r="E9" s="36">
         <f>IF(B9="","",SUMPRODUCT((Transaktionen!D$4:D$500="Einnahme")*(Transaktionen!G$4:G$500=B9)*Transaktionen!E$4:E$500))</f>
@@ -5321,8 +6351,8 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="29"/>
       <c r="E10" s="29">
         <f>IF(B10="","",SUMPRODUCT((Transaktionen!D$4:D$500="Einnahme")*(Transaktionen!G$4:G$500=B10)*Transaktionen!E$4:E$500))</f>
@@ -5337,8 +6367,8 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36">
         <f>IF(B11="","",SUMPRODUCT((Transaktionen!D$4:D$500="Einnahme")*(Transaktionen!G$4:G$500=B11)*Transaktionen!E$4:E$500))</f>
@@ -5538,158 +6568,158 @@
   <sheetData>
     <row r="1" ht="50" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="83" t="s">
-        <v>110</v>
+      <c r="B1" s="84" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="84" t="s">
-        <v>111</v>
+      <c r="B2" s="85" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="86" t="s">
-        <v>112</v>
+      <c r="B4" s="87" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="87" t="s">
-        <v>113</v>
+      <c r="B6" s="88" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="85" t="s">
-        <v>114</v>
+      <c r="B7" s="86" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="88" t="s">
-        <v>115</v>
+      <c r="B8" s="89" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="87" t="s">
-        <v>116</v>
+      <c r="B10" s="88" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="85" t="s">
-        <v>117</v>
+      <c r="B11" s="86" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="88" t="s">
-        <v>118</v>
+      <c r="B12" s="89" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="87" t="s">
-        <v>119</v>
+      <c r="B14" s="88" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="85" t="s">
-        <v>120</v>
+      <c r="B15" s="86" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="88" t="s">
-        <v>121</v>
+      <c r="B16" s="89" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="87" t="s">
-        <v>122</v>
+      <c r="B18" s="88" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="85" t="s">
-        <v>123</v>
+      <c r="B19" s="86" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="88" t="s">
-        <v>124</v>
+      <c r="B20" s="89" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="87" t="s">
-        <v>125</v>
+      <c r="B22" s="88" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="85" t="s">
-        <v>126</v>
+      <c r="B23" s="86" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="88" t="s">
-        <v>127</v>
+      <c r="B24" s="89" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="89" t="s">
-        <v>128</v>
+      <c r="B26" s="90" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">

--- a/budget-tracker/Budget-Tracker.xlsx
+++ b/budget-tracker/Budget-Tracker.xlsx
@@ -1509,7 +1509,7 @@
             <c:numRef>
               <c:f>Dashboard!$C$39:$C$46</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00\ "\u20ac"</c:formatCode>
+                <c:formatCode>#,##0.00\ "€"</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1674,7 +1674,7 @@
                   <c:v>Feb</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>M\u00e4r</c:v>
+                  <c:v>Mär</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Apr</c:v>
@@ -1710,7 +1710,7 @@
             <c:numRef>
               <c:f>Dashboard!$C$13:$C$24</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00\ "\u20ac"</c:formatCode>
+                <c:formatCode>#,##0.00\ "€"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1787,7 +1787,7 @@
                   <c:v>Feb</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>M\u00e4r</c:v>
+                  <c:v>Mär</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Apr</c:v>
@@ -1823,7 +1823,7 @@
             <c:numRef>
               <c:f>Dashboard!$D$13:$D$24</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00\ "\u20ac"</c:formatCode>
+                <c:formatCode>#,##0.00\ "€"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1916,7 +1916,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="#,##0\ &quot;\u20ac&quot;" sourceLinked="0"/>
+        <c:numFmt formatCode="#,##0\ &quot;€&quot;" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
